--- a/new original/_Lang_Chinese/Lang/CN/Data/god_talk.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Data/god_talk.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="396">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t xml:space="preserve">…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umimya-!</t>
   </si>
   <si>
     <t xml:space="preserve">Welcome, welcome. I will ensure that you are never bored.</t>
@@ -777,6 +774,39 @@
 Oh my, I hope my brother takes a liking to you…</t>
   </si>
   <si>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A foolish institution. Very well, I shall celebrate it just for today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tying yourself down like that? How ridiculous, kitten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In my name, I bestow my blessing upon you both.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be happy! Happy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muwahahahahaha!!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I-I'm not jealous or anything. ...stupid...congratulations...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never let go...never...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have my blessing. I shall refrain from mischief—just for today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oh my, how very delightful! Congratulations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I give you my congratulations. A fine achievement for your race.</t>
+  </si>
+  <si>
     <t xml:space="preserve">是新信徒吗。好好努力，不要让我的名字蒙羞。</t>
   </si>
   <si>
@@ -799,9 +829,6 @@
   </si>
   <si>
     <t xml:space="preserve">是么，反正你也会背叛我的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜喵喵！</t>
   </si>
   <si>
     <t xml:space="preserve">哎呀呀，欢迎你的到来。我会注意不让你感到无聊的。</t>
@@ -1387,6 +1414,9 @@
     <t xml:space="preserve">快些醒来。</t>
   </si>
   <si>
+    <t xml:space="preserve">呜喵喵！</t>
+  </si>
+  <si>
     <t xml:space="preserve">呼哈哈哈哈哈哈！</t>
   </si>
   <si>
@@ -1423,6 +1453,36 @@
   <si>
     <t xml:space="preserve">你要去哥哥那里吗？记得不能失了礼数。
 哎呀，希望哥哥他能喜欢你…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然是愚蠢的制度，但今天就给你祝福吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作茧自缚。你这家伙，真蠢啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以吾之名赐福于汝等。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一定要幸福哦！一定哦！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼哈哈哈哈哈哈！！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">才、才没有嫉妒呢！恭、恭喜你…笨蛋…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要一直珍惜...永不分离...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">祝福你。今天就不搞恶作剧了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎呀，真是可喜可贺呢！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恭喜你，进展不错。</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1587,7 @@
       <protection locked="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
       <alignment/>
       <protection locked="1"/>
@@ -1580,6 +1640,14 @@
       <alignment wrapText="1"/>
       <protection locked="1"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1604,9 +1672,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1341360</xdr:colOff>
+      <xdr:colOff>1340640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>154080</xdr:rowOff>
+      <xdr:rowOff>153360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1616,7 +1684,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1341360" cy="154080"/>
+          <a:ext cx="1340640" cy="153360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1649,9 +1717,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1341360</xdr:colOff>
+      <xdr:colOff>1340640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>154080</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1661,7 +1729,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1341360" cy="154800"/>
+          <a:ext cx="1340640" cy="154080"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
@@ -1691,9 +1759,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1172880</xdr:colOff>
+      <xdr:colOff>1172160</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>33480</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1703,7 +1771,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1172880" cy="358560"/>
+          <a:ext cx="1172160" cy="357840"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
@@ -1926,892 +1994,939 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>213</v>
+      <c r="J3" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="O3" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.45">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>213</v>
+      <c r="J4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="O4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="23.85">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>213</v>
+      <c r="J5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="O5" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="23.85">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>213</v>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="23.85">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>213</v>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="O7" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="23.85">
       <c r="A8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>213</v>
+      <c r="J8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="O8" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="23.85">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>213</v>
+      <c r="J9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="O9" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="23.85">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>213</v>
+      <c r="J10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="O10" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="23.85">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>213</v>
+      <c r="J11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="O11" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="35.05">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>213</v>
+      <c r="J12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="O12" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="57.45">
       <c r="A13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>213</v>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="O13" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="102.2">
       <c r="A14" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>213</v>
+      <c r="J14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="O14" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" ht="91">
       <c r="A15" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>213</v>
+      <c r="J15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="O15" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" ht="35.05">
       <c r="A16" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>213</v>
+      <c r="J16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="O16" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" ht="35.05">
       <c r="A17" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>213</v>
+      <c r="J17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="O17" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" ht="23.85">
       <c r="A18" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>213</v>
+      <c r="J18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="O18" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" ht="12.75">
       <c r="A19" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>213</v>
+        <v>373</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>213</v>
+      <c r="J19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" ht="12.75">
       <c r="A20" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>213</v>
+      <c r="J20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="O20" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="21" ht="22.35">
+    <row r="21" ht="32.8">
       <c r="A21" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="O21" t="s">
-        <v>217</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" ht="12.75">
+      <c r="A22" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="O22" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="1048576" ht="12.8"/>

--- a/new original/_Lang_Chinese/Lang/CN/Data/god_talk.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Data/god_talk.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId3"/>
+    <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="ExcelA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="215">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -805,684 +805,6 @@
   </si>
   <si>
     <t xml:space="preserve">I give you my congratulations. A fine achievement for your race.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是新信徒吗。好好努力，不要让我的名字蒙羞。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你做了一个正确的选择呢，我会好好疼爱你的，我的小猫咪。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">努力回应吾的期待吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇～你真的要信我？真的信我？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈！你逃不掉了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人、人家才没在期待你的活跃呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">来的好…我期待…你的表现。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是么，反正你也会背叛我的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀呀，欢迎你的到来。我会注意不让你感到无聊的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，这又是谁来了呢？如果你信奉我的话，我也会好好待你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是入信者吗？真的有你这样好奇心旺盛的人啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">相当不错的礼物。
-我就收下吧。
-不错。我要夸奖你。
-很好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，很会讨好我嘛。如此大献殷勤，你安的是什么心呢？
-真是个机灵的家伙。
-不错，向我献上更多吧。
-啊哈哈哈！更多，更多！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">十分感谢汝的祭品。
-嗯，此等心意难能可贵。
-凡人啊，吾当为汝道谢。
-汝堪称信徒之楷模。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜喵喵！
-呜喵喵喵喵喵！
-哇哦♪
-好东西！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈—！
-呼哈哈哈！
-呼哈哈哈哈，好啊！
-呼哈哈哈哈哈哈哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人、人家才没觉得高兴呢！
-要、要给我吗？
-我、我可不会跟你说谢谢！
-笨、笨蛋！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">十分感谢…真的…很不错。
-这个…很不错。
-那我就…收下了。
-不错的礼物…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这样一来我不收下也不是了。
-品味还不错嘛。
-我都被你的热情给感动到了。
-那我可就笑纳了。感谢你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">可爱的仆从啊，感谢你。
-哎呀，真厉害！
-你的奉献总能让我心头感到温暖。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，这是很好的礼物。我心怀感激地接受了。
-谢谢你的礼物，不过记得要把钱花在提升装备上哦？
-很有趣的东西。谢谢你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是我忠诚的仆人，拿去，好好使用它。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是赏给你这个仆人的，要好好的珍惜使用，懂了么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">作为对汝忠诚的回报，将此物赐予汝吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这个给你…要珍惜哦！珍惜哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈！收下吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这、这个才不是人家专门为你准备的呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好东西…送给你…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你给我带来了不少乐趣。我也是时候该给你一些奖励了吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我也得为自己重要的仆从予以回报才行呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是时候给你奖励了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很有胆量嘛，你这可耻的叛徒！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼哼，蠢货！离开我你还能活下去吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当真背叛吾？愚蠢至极。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜喵喵！真的要背叛我了？真的？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼呼呼呼呼哈哈哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什、什么嘛，你这样的家伙，即使不在了人家也不会感到寂寞的呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">背叛…绝不原谅…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这就要离开了吗？好遗憾啊，明明还有很多乐趣在等着我们呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，你要走了吗。我好伤心…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我本来很中意你的。那么，就让我像正经的神明那样给你降下天罚。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">挺能干的嘛，我对你刮目相看了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">表扬一下你吧，我可爱的小洋娃娃。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很好，吾会记住汝的所行的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇哦♪好开心喵！喜欢你！真喜欢你！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈，很好很好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什、什么啊，人、人家才不会夸奖你呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">做的不错…真的…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是我最喜欢的人。至少现在是这样的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">做得真好。让我摸摸你的头吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯。你的侍奉很不错。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你真是干了件蠢事。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你这胆大妄为的垃圾，我可得好好惩罚你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">汝将会为愚昧的尝试付出代价的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">笨蛋笨蛋笨蛋！笨蛋！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈，太弱了太弱了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你、你做了什么啊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">敌人…不会轻饶…绝对。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你如此大胆的尝试真的很有趣哦。不过结果有些遗憾呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你很勇敢呢…不过你真的以为能赢得了我吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，半吊子可不好啊。让我给你施以相应的报复吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你可谓是信徒们的榜样。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是我最喜欢的奴隶。不管到了哪里都不可忘记要为我尽力。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已经很久都没有人有资格担负吾的名讳了。但若是汝，或许…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">心儿怦怦跳了。我喜欢你哦。喜欢哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈哈哈！愉悦愉悦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">讨、讨厌啦，人、人家才没有喜欢你呢，笨蛋！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是…我重要的仆人…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…你是我的…算了，还是不说这种无趣的话了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想摸我的尾巴？呵呵呵，可以哦。来摸吧～。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在我观察你的时候，时间总是过的很快。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是我最喜欢的仆人。把你的灵魂奉献给我，我也将尽力永远保护你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">服从我。将你的身心全部交付给我。要是有哪个猪猡胆敢划伤你漂亮的小脸蛋，我定会将其碾成肉糜。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">令人惊叹，凡人。汝乃是尘世间唯一可得吾信赖之人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">爱你！爱你爱你爱你！最爱你了！我们到死都要在一起哦！在一起哟！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈哈！呼哈哈哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人、人家才没有爱上你呢！不要离开我身边！你这笨蛋…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你会和我…永远在一起吧？再也不会放走你…直到你死去。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真是输给你了，你就是我最爱的仆从。满足了吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快来这里，我最爱的仆从。让我用尾巴把你卷起来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我从不偏袒，但只有你是特别的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回来了吗。真是意外，还是个有骨气的家伙。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你到哪里闲逛去了。看来还得更多的调教调教你呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凡人哟，汝回来了啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">喵喵？你回来了？回来了？等好久了哟！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈！欢迎回来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人、人家才没有在等你回来呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎回来…等你很久了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我不在的时候你感到寂寞了吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎回来。我可以抱抱你哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">刚好想见识你大闹一场了。不要让我失望哦？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">血肉之躯的不便与悲哀之处就是不得不将短暂生命中大量时间都浪费在睡觉这件事上。不过为了能让你继续服侍我，现在你就好好休息吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好吧，那我就暂时把你颈上的枷锁松开，尽情地享受难得的休息吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">尽情恢复旅途的疲劳吧，吾那不灭的赤炎将保护汝，使汝不被那些借助夜幕潜入的邪恶者打扰。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要睡了？真的要睡了？晚安！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈！我会一直跟着你的，一直到你的梦中。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">晚、晚安的吻什么的…人家绝对不要啦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">晚安…明天…新的芽儿将蓬勃的生长。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">多么安稳的睡颜。愿你的人生如梦一般灿烂。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在月影下安心沉眠吧。有我守护着你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好好休息吧。想要跨越苦难，必须充足地休息。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不错。
-你难道不想继续将其进一步再进行分解吗？
-那份灵魂将会成为一个新机器的上好部件。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好脏啊。不把血擦干净可不行呢。
-啊哈哈！绞碎吧绞碎吧！
-嘛啊，真是不听话的小猫咪。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">做的不错。
-而此魂灵将归于元素。
-高声颂唱吾名吧，以吾之烈焰给予亡者安息。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还要玩！还要玩！
-死掉了哟！死了哟！
-呜喵—呜喵喵。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈！
-死吧！死吧！呼哈哈哈哈！
-喝哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很、很厉害嘛。
-停、停手啊。真讨厌
-不要过来！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">弄脏了呢。
-适可而止。
-…这就是…你所期待的结果？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你也露了一手呢。
-哎呀呀，这剩下的摊子要谁来收拾呢？
-你真的不会让我感到无聊呢。
-做得好！我为你感到骄傲。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，真是个好孩子！
-哎呀哎呀，不可以恶作剧哦。
-哎呀，好厉害呢。
-你很有精神呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不错嘛！果然争斗就要这样才行。
-嗯，水平很不错。真是赏心悦目。
-杀得好！
-呵呵，你能感到自己在飞速成长吧？
-踏实地积累了经验啊。这可是很了不起的！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你也把身体机械化怎么样？
-你的所为不可让我蒙羞。
-不要焦急。很快，一切由机械支配的时代就要到来了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">悲惨的猪猡们。
-玛尼？敢再说出那个名字的话就切碎你哦，小猫咪。
-我把上一个仆人撕碎后丢给风精灵做饲料了，因为我有点讨厌他的发型。哈哈！
-风声是我的孩子， 不能被任何事所束缚哦。你也一样。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">汝不可大意。
-吾等所背负的痛苦，凡人是不会理解的。
-吾名为伊兹帕鲁特。乃元素之起源，统御太古火焰之王，众神之主。
-众神的战争远未结束。那一刻到来之时，汝将效命于吾之帐下。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">帝王蟹！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什、什么啊笨蛋！
-我真的适合这份工作吗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">树木在轻语…森林在奏响生命的歌谣…用心去倾听吧…
-这世上的明争暗斗，真是…丑陋啊。
-我的艾赫卡托尔…现在已经…面目全非了。
-我所能给予的…远比你能掠夺的要多得多。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">向我祈祷的话，有时会得到祝福，有时会得到诅咒哦。
-这么勇敢，竟然敢向我搭话。还是说，你已经大难临头了呢？
-好了，别再让我感到无聊了。
-我当然会倾听祈祷。但是我是否会去回应就另当别论啦。
-穗罗女还是那么孩子气呢。似乎到现在都会把糖果当祭品收下。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不要惧怕黑暗。月光一定会引导你。
-我一直都在守护着你。
-在呢在呢，我在听着你的祈祷。
-哎呀，怎么了吗？有什么需要我帮助的事吗？
-吉须阿弥是位可靠的兄长，不过有时也会有些小小的坏心眼。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，有时信仰会决定成败。只要你祈求，我就给予你帮助。
-需要我的力量吗？
-给予你战祸的加护。
-是不是欺负太多弱小的家伙了？记得要找强敌战斗哦？
-停滞会招致腐败。所以适度的刺激是必须的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">文明的进步，总是为人类带来对自己的失望。
-我那留在下界的一部分身体似乎还没有腐朽。真令人吃惊啊。
-怎么了？你在偷懒吗？
-你不觉得祈祷等完全是种不合理的行为吗？
-被机械统治才是人类的救赎。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，还知道要向我祈祷，算你有心了呢。
-你想知道风的名字吗？
-果然是垃圾呢。你有空祈祷还不如去干活。
-你是想被我千刀万剐呢？还是说，想要被穿·成·一·串呢？
-为我尽心尽力吧，小猫咪。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">汝之言行，皆为编织命运的丝线。
-吾之目与汝同在。
-汝之灵魂终将回归元素。
-汝之祈祷，传入吾耳。
-并非言辞，要用行动赞颂吾。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜喵？
-祈祷…？想要什么吗？呜咪？
-喵！吓了我一跳！恶作剧要适可而止哟！
-请不要忘记我，一直要在一起哟！
-下次再一起玩吧！
-呜咪呀。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈！
-打算妨碍我入睡吗？呼哈哈哈！
-和我来较量较量吧？呼哈哈哈！
-呼哈哈！
-我可不会听你矫情。
-呼哈哈哈哈。来锻炼吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什、什么啊，怎么了…？
-累了吗？来、来人家这里，稍微休息一下吧！
-我是朱亚，带来治愈之神…
-防卫者…？喂，你去哪里了？防卫者！
-治愈疲惫的灵魂是我的工作。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">感受到了吗…大地的恩惠…？
-你的祈祷…传达到了…
-我一直在注视着…你的行为。
-是吗…你在我身边…
-生命的萌生…与枯萎…我只是见证着这一切…
-花也好…你也好…最后都会…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">让我来帮你一把。
-没什么好烦恼的。只要相信狐狸就好了。
-你真让我感到惊讶。接下来你又会怎么做呢？
-你成功勾起了我的兴趣。可不要枉费我对你的关注哦。
-无论岁月如何变迁，穗罗女永远是我可爱的妹妹。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯？想摸我的尾巴？真拿你没办法呢。
-你有在努力呢。我全都看在眼里。
-我有两个哥哥…不，是曾经有过…尤芙已经…
-没关系没关系。我不会让任何人伤到你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你只需在自己的道路上前行即可。我会满怀兴趣地守望。
-我很尊重库米罗妮和小朱亚哦。后勤补给和医疗对战争来说非常重要。
-你问眼睛上的伤？这是像勋章一样的东西。
-看到你的表现，就让我想要重回战场了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这个破零件就送给你吧。
-这也许对你有些用处。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拿去吧，这是个给你的奖赏。爬在地上捡起来吧。
-到吃饭的时间了哦，小猫咪。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吾将赐予汝一份微薄的奖赏。
-好好利用它。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这个，给你！
-呜喵？要吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈。用这个！
-接好了，要扔过去了！呼哈哈哈哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咦…？没、没什么…
-只是刚好有多余的而已。不要搞错了哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">将这种子…托付于你…好好待它。
-对了…这个…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">收下这个，希望你看到它就能想起我。
-哎呀呀，你就这么想要它吗？好吧好吧，那就给你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我可爱的仆从，赠于你合适的礼物。
-听好了，可不能弄丢哦？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你一定可以好好使用它吧？
-我很期待，你会怎样使用它。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">来吧，化为风吧！
-去吧！
-啊哈哈！把他千刀万剐吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吾以火焰点燃汝之灵魂。
-赐予汝元素的加护。
-接受它吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">为身负此伤的灵魂照耀治愈之光！
-站起来吧！
-活下去吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人造人，今后让这个凡人负责你的维护如何？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">去跟着此人吧，黑天使。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">流放者啊，去此人身边赎罪吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">来吧，一起来玩吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈，有趣！就跟着这个人走吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">防卫者，去保护那个#pc_race吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">走好…小妖精。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的女儿啊，请你好好侍奉这为我效力之人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的狐女仆啊，去好好照料他吧，就如侍奉我一般。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">去为此人效力吧。别担心，你办事我放心。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快起床。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊哈哈，好可爱的睡颜啊，小猫咪。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快些醒来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜喵喵！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈哈哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快、快起来嘛！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">早上好…睡得还好吗…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好啊，用吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你想要？那就来求我呀。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赐予汝一点吾之神力。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜喵喵！被找到了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈哈！用吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这、这样可以吗？…好吧，我抱——…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">把它…送给你…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对我的妹妹好一些吧。她可是个非常善良的孩子。
-如果要去穗罗女那里的话，能帮我送些点心吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你要去哥哥那里吗？记得不能失了礼数。
-哎呀，希望哥哥他能喜欢你…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然是愚蠢的制度，但今天就给你祝福吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">作茧自缚。你这家伙，真蠢啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">以吾之名赐福于汝等。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一定要幸福哦！一定哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼哈哈哈哈哈哈！！！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">才、才没有嫉妒呢！恭、恭喜你…笨蛋…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要一直珍惜...永不分离...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">祝福你。今天就不搞恶作剧了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，真是可喜可贺呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恭喜你，进展不错。</t>
   </si>
 </sst>
 </file>
@@ -1504,19 +826,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1550,7 +872,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -1559,94 +881,94 @@
     </border>
   </borders>
   <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1656,13 +978,13 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in Normal" xfId="20" builtinId="0"/>
+    <cellStyle name="Excel Built-in Normal" xfId="20"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1676,7 +998,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>153360</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="0" name="Rectangle 2" hidden="1"/>
         <xdr:cNvSpPr/>
@@ -1690,7 +1012,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -1721,7 +1043,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>154080</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="1" name="AutoShape 2"/>
         <xdr:cNvSpPr/>
@@ -1732,7 +1054,7 @@
           <a:ext cx="1340640" cy="154080"/>
         </a:xfrm>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -1763,7 +1085,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="AutoShape 2"/>
         <xdr:cNvSpPr/>
@@ -1774,7 +1096,7 @@
           <a:ext cx="1172160" cy="357840"/>
         </a:xfrm>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -1902,32 +1224,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O1048576"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.14" style="1" customWidth="1"/>
-    <col min="2" max="2" width="44.42" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.71" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42" style="1" customWidth="1"/>
-    <col min="6" max="6" width="51" style="1" customWidth="1"/>
-    <col min="7" max="7" width="46.57" style="1" customWidth="1"/>
-    <col min="8" max="8" width="47" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.96" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.79" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.51" style="1" customWidth="1"/>
-    <col min="12" max="12" width="52.71" style="1" customWidth="1"/>
-    <col min="13" max="13" width="69.54" style="1" customWidth="1"/>
-    <col min="14" max="14" width="78.05" style="1" customWidth="1"/>
-    <col min="16" max="16381" width="14.42" style="1"/>
-    <col min="16382" max="16384" width="11.53" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="41.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="46.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="52.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="69.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="78.05"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="16" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1972,7 +1294,7 @@
       </c>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" ht="12.8">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1989,77 +1311,74 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.2">
+    <row r="3" s="1" customFormat="true" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>222</v>
+        <v>22</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>223</v>
+        <v>23</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>224</v>
+        <v>24</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="O3" t="s">
-        <v>226</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="57.45">
+    <row r="4" s="1" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>229</v>
+        <v>29</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>230</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>231</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>232</v>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>22</v>
@@ -2071,42 +1390,39 @@
         <v>22</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>234</v>
+        <v>34</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="O4" t="s">
-        <v>226</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="23.85">
+    <row r="5" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>238</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>241</v>
+        <v>42</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>243</v>
+        <v>44</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>22</v>
@@ -2118,42 +1434,39 @@
         <v>22</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>244</v>
+        <v>45</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>245</v>
+        <v>46</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="O5" t="s">
-        <v>226</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="23.85">
+    <row r="6" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>247</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>248</v>
+        <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>249</v>
+        <v>51</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>250</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>251</v>
+        <v>53</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>252</v>
+        <v>54</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>253</v>
+        <v>55</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>22</v>
@@ -2165,42 +1478,39 @@
         <v>22</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>254</v>
+        <v>56</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>255</v>
+        <v>57</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="O6" t="s">
-        <v>226</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="23.85">
+    <row r="7" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>257</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>258</v>
+        <v>61</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>259</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>260</v>
+        <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>261</v>
+        <v>64</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>262</v>
+        <v>65</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>263</v>
+        <v>66</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>22</v>
@@ -2212,42 +1522,39 @@
         <v>22</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>265</v>
+        <v>68</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="O7" t="s">
-        <v>226</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="23.85">
+    <row r="8" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>268</v>
+        <v>72</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>269</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>270</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>272</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>22</v>
@@ -2259,42 +1566,39 @@
         <v>22</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>274</v>
+        <v>78</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="O8" t="s">
-        <v>226</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="23.85">
+    <row r="9" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>279</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>281</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>282</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>283</v>
+        <v>88</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>22</v>
@@ -2306,42 +1610,39 @@
         <v>22</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>284</v>
+        <v>89</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>285</v>
+        <v>90</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="O9" t="s">
-        <v>226</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="23.85">
+    <row r="10" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>288</v>
+        <v>94</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>290</v>
+        <v>96</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>291</v>
+        <v>97</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>292</v>
+        <v>98</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>293</v>
+        <v>99</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>22</v>
@@ -2353,42 +1654,39 @@
         <v>22</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>294</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="O10" t="s">
-        <v>226</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="23.85">
+    <row r="11" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>297</v>
+        <v>104</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>298</v>
+        <v>105</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>299</v>
+        <v>106</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>300</v>
+        <v>107</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>301</v>
+        <v>108</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>302</v>
+        <v>109</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>303</v>
+        <v>110</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>22</v>
@@ -2400,42 +1698,39 @@
         <v>22</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>304</v>
+        <v>111</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>305</v>
+        <v>112</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="O11" t="s">
-        <v>226</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="35.05">
+    <row r="12" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>308</v>
+        <v>116</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>309</v>
+        <v>117</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>310</v>
+        <v>118</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>311</v>
+        <v>119</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>312</v>
+        <v>120</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>313</v>
+        <v>121</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>22</v>
@@ -2447,42 +1742,39 @@
         <v>22</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>314</v>
+        <v>122</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>315</v>
+        <v>123</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="O12" t="s">
-        <v>226</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="57.45">
+    <row r="13" s="1" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>317</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>318</v>
+        <v>127</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>319</v>
+        <v>128</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>320</v>
+        <v>129</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>322</v>
+        <v>131</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>323</v>
+        <v>132</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>22</v>
@@ -2494,42 +1786,39 @@
         <v>22</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>324</v>
+        <v>133</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>325</v>
+        <v>134</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="O13" t="s">
-        <v>226</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="102.2">
+    <row r="14" s="1" customFormat="true" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>327</v>
+        <v>137</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>328</v>
+        <v>138</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>329</v>
+        <v>139</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>330</v>
+        <v>140</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>331</v>
+        <v>141</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>332</v>
+        <v>142</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>333</v>
+        <v>143</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>22</v>
@@ -2541,42 +1830,39 @@
         <v>22</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>334</v>
+        <v>144</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>335</v>
+        <v>145</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="O14" t="s">
-        <v>226</v>
+        <v>146</v>
       </c>
     </row>
-    <row r="15" ht="91">
+    <row r="15" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
         <v>147</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>337</v>
+        <v>148</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>338</v>
+        <v>149</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>339</v>
+        <v>150</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>340</v>
+        <v>151</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>341</v>
+        <v>152</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>342</v>
+        <v>153</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>343</v>
+        <v>154</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>22</v>
@@ -2588,42 +1874,39 @@
         <v>22</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>344</v>
+        <v>155</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>345</v>
+        <v>156</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="O15" t="s">
-        <v>226</v>
+        <v>157</v>
       </c>
     </row>
-    <row r="16" ht="35.05">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
         <v>158</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>347</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>348</v>
+        <v>160</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>349</v>
+        <v>161</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>350</v>
+        <v>162</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>351</v>
+        <v>163</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>352</v>
+        <v>164</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>353</v>
+        <v>165</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>22</v>
@@ -2635,43 +1918,32 @@
         <v>22</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>355</v>
+        <v>167</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="O16" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="17" ht="35.05">
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>226</v>
-      </c>
+      <c r="B17" s="6"/>
       <c r="C17" s="4" t="s">
-        <v>357</v>
+        <v>170</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>226</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
       <c r="G17" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>226</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
         <v>22</v>
       </c>
@@ -2682,42 +1954,35 @@
         <v>22</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="O17" t="s">
-        <v>226</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
     </row>
-    <row r="18" ht="23.85">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>360</v>
+        <v>175</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>361</v>
+        <v>176</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>362</v>
+        <v>177</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>363</v>
+        <v>178</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>364</v>
+        <v>179</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>365</v>
+        <v>180</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>366</v>
+        <v>181</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>22</v>
@@ -2729,42 +1994,39 @@
         <v>22</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>367</v>
+        <v>182</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>368</v>
+        <v>183</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="O18" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="19" ht="12.75">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>185</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>370</v>
+        <v>186</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>371</v>
+        <v>187</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>372</v>
+        <v>188</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>373</v>
+        <v>189</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>374</v>
+        <v>190</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>375</v>
+        <v>191</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>376</v>
+        <v>192</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>22</v>
@@ -2775,43 +2037,34 @@
       <c r="K19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L19" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="O19" t="s">
-        <v>226</v>
-      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
     </row>
-    <row r="20" ht="12.75">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>193</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>377</v>
+        <v>194</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>378</v>
+        <v>195</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>379</v>
+        <v>196</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>380</v>
+        <v>197</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>381</v>
+        <v>198</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>382</v>
+        <v>199</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>383</v>
+        <v>200</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>22</v>
@@ -2822,90 +2075,56 @@
       <c r="K20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L20" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="O20" t="s">
-        <v>226</v>
-      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
     </row>
-    <row r="21" ht="32.8">
+    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>226</v>
-      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
       <c r="L21" s="7" t="s">
-        <v>384</v>
+        <v>202</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="O21" t="s">
-        <v>226</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N21" s="6"/>
     </row>
-    <row r="22" ht="12.75">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>386</v>
+        <v>205</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>387</v>
+        <v>206</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>388</v>
+        <v>207</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>389</v>
+        <v>208</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>390</v>
+        <v>209</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>391</v>
+        <v>210</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>392</v>
+        <v>211</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>22</v>
@@ -2917,24 +2136,21 @@
         <v>22</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>393</v>
+        <v>212</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>394</v>
+        <v>213</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="O22" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="1048576" ht="12.8"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
